--- a/Excel/AICodeKing.xlsx
+++ b/Excel/AICodeKing.xlsx
@@ -463,25 +463,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>67Lw_hRRAyw</t>
+          <t>P8luPmEa1QI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemini 3.0 Pro (Early Checkpoint - Tested): OH MY GOD! IT'S #1 &amp; This IS THE CRAZIEST SOTA Mod</t>
+          <t>OpenCode + Gemini 2.5 Pro: BYE Claude Code! I'm SWITCHING To the FASTEST AI Coder!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>48526</v>
+        <v>56669</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0:08:30</t>
+          <t>0:11:11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,25 +493,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OzGnko58w4Q</t>
+          <t>uuV1DcvObsg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gemini 3 Pro (Fully Tested): This MODEL Broke MY BENCHMARKS! Better than X58 &amp; BEST AI CODER Y</t>
+          <t>Oh My OpenCode (5 SUPER Agent/MCP/Prompt Config): This makes OPENCODE - A BEAST! REALLY GOOD A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38575</v>
+        <v>50757</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0:08:02</t>
+          <t>0:13:28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,25 +523,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_rR4szKm9dQ</t>
+          <t>UQv-OfWDgxs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gemini CLI 5.0 (New Upgrades): Get Ready for Gemini 3! New Code Sub-Agents, Shell Options!</t>
+          <t>OpenCode + Free Opus 4.5 (Antigravity Auth) : STOP USING Claude Code MAX This is the NEW ALTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37343</v>
+        <v>42875</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0:09:05</t>
+          <t>0:09:56</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,25 +553,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3x6Bnel13NY</t>
+          <t>uiCBAAJahGI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gemini 3 PRO ULTRA MODE (KingMode Prompt): This SIMPLE TRICK MAKES Gemini 3 PRO - A BEAST!</t>
+          <t>Free Unlimited Qwen-3 Coder API + Roo,Cline,OpenCode: This is the BEST FREE AI Coder Right Now</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33183</v>
+        <v>28112</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0:13:24</t>
+          <t>0:08:01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,25 +583,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>_rKybKSmiLs</t>
+          <t>bdNf-KieKTY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gemini 3.0 Flash + Opus 4.5 + Antigravity: This ALMOST-UNLIMITED FREE AI Coding Workflow is SO</t>
+          <t>Unlimited Free APIs (GLM-5,Kimi-K2.5,MiniMax) + OpenCode,OpenClaw: This FULLY FREE Coder is CR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28716</v>
+        <v>27903</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0:08:05</t>
+          <t>0:09:18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -613,25 +613,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y5LJF4rKylc</t>
+          <t>J2thowAjPM0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Google Antigravity + FREE Opus 4.5 &amp; Gemini 3: This CRUSHES Cursor for FREE! CRAZY FREE Altern</t>
+          <t>Ralphy + OpenCode, Claude Code: This is RALPH LOOPS ON STEROIDS!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27157</v>
+        <v>24498</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0:08:13</t>
+          <t>0:09:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,25 +643,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ka9XAAOnnw0</t>
+          <t>RlEKs4JAMqw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.0 (X58 New Checkpoint TESTED): Google launched a new Checkpoint for Gemini 3 &amp; I TEST</t>
+          <t>OpenCode Desktop: RIP Claude Code? Is it REALLY SPECIAL?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21654</v>
+        <v>23653</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0:09:16</t>
+          <t>0:08:21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -673,25 +673,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vEjQ4w9j_dc</t>
+          <t>hv0V0GJpC78</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gemini CLI 4.0 : This INTERFACE is now better than Claude Code! This w/ Gemini 3 will be INSAN</t>
+          <t>Pi Coding Agent: RIP Claude Code &amp; OpenCode! This Opensource Coding Agent is JUST WAY BETTER!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21107</v>
+        <v>23281</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0:10:38</t>
+          <t>0:14:08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -703,25 +703,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dEOYxDGjAww</t>
+          <t>Xv5p4i-I4es</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google AI Studio Coder 2.0: Ready for Gemini 3! Google just Leveled-up their FULLY FREE AI Cod</t>
+          <t>SST-OpenCode: REPLACE Claude Code Now! (Works w/ Claude Max &amp; Pro Plan)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20429</v>
+        <v>17270</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0:09:33</t>
+          <t>0:08:40</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -733,25 +733,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5s0mfKU2iFM</t>
+          <t>bWKHPelgNgs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.2 (V/S Gemini 3 &amp; Opus 4.5) - Fully Tested: Is it the OPENAI Comeback or A FLOP?</t>
+          <t>Claude Code / OpenCode + T-Mux + Worktrees: This SELF-SPAWNING AI Coder TEAM is INSANITY!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19848</v>
+        <v>16345</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0:17:33</t>
+          <t>0:11:13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
